--- a/data/trans_bre/P2A_psíq_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,92</t>
+          <t>-3,14; 0,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 2,54</t>
+          <t>-4,96; 2,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 2,32</t>
+          <t>-3,28; 2,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,12</t>
+          <t>-0,45; 4,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,02; 110,9</t>
+          <t>-74,3; 108,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-80,26; 259,67</t>
+          <t>-86,4; 208,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 1278,5</t>
+          <t>-53,98; 1214,08</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,19</t>
+          <t>1,02; 4,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,41</t>
+          <t>-1,68; 1,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,74</t>
+          <t>-0,11; 1,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,72</t>
+          <t>-2,09; 2,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,4; —</t>
+          <t>13,68; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 330,76</t>
+          <t>-81,69; 265,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 185,13</t>
+          <t>-52,02; 171,65</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,1</t>
+          <t>-1,34; 1,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,7</t>
+          <t>-3,88; 1,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,32</t>
+          <t>0,36; 2,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,83</t>
+          <t>-1,72; 1,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-79,94; 172,02</t>
+          <t>-84,34; 150,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 177,91</t>
+          <t>-58,8; 185,69</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 1,0</t>
+          <t>-2,2; 0,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,31</t>
+          <t>-0,14; 3,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,8</t>
+          <t>-1,32; 4,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,13</t>
+          <t>0,28; 2,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 299,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 1063,44</t>
+          <t>-29,87; 1048,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 271,18</t>
+          <t>-38,91; 274,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,59; —</t>
+          <t>-8,8; —</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,68</t>
+          <t>-1,68; 2,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,35</t>
+          <t>-3,68; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,55</t>
+          <t>-1,0; 3,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,27</t>
+          <t>-2,24; 0,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-71,57; 223,83</t>
+          <t>-69,39; 242,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-1,87; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,09</t>
+          <t>-1,45; 3,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,73</t>
+          <t>-0,37; 2,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,62</t>
+          <t>-2,88; 2,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 494,53</t>
+          <t>-62,86; 684,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,22; 125,16</t>
+          <t>-51,74; 101,73</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,91</t>
+          <t>-0,94; 0,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,99</t>
+          <t>-1,58; 1,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,33</t>
+          <t>-0,49; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 55,98</t>
+          <t>1,02; 61,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-80,14; 380,52</t>
+          <t>-82,52; 346,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-71,33; 101,02</t>
+          <t>-68,5; 118,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-74,4; —</t>
+          <t>-72,36; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,64; 2267,68</t>
+          <t>23,2; 2420,22</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,26</t>
+          <t>-0,97; 1,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,34</t>
+          <t>-0,28; 2,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,78</t>
+          <t>-0,5; 1,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,83</t>
+          <t>-0,61; 1,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,69; 306,42</t>
+          <t>-66,01; 274,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,33; 572,79</t>
+          <t>-32,38; 560,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,36; 379,64</t>
+          <t>-43,76; 314,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 245,48</t>
+          <t>-28,39; 286,55</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,77</t>
+          <t>-0,26; 0,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,94</t>
+          <t>-0,47; 0,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,21</t>
+          <t>0,09; 1,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 23,22</t>
+          <t>0,4; 23,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 109,91</t>
+          <t>-23,31; 118,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-23,3; 64,93</t>
+          <t>-21,19; 57,91</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,55; 179,03</t>
+          <t>7,09; 167,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21,85; 1267,66</t>
+          <t>18,79; 1251,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>157,94%</t>
+          <t>72,75%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,92</t>
+          <t>-3,06; 0,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,45</t>
+          <t>-4,55; 2,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,09</t>
+          <t>-3,25; 2,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,42</t>
+          <t>-0,95; 3,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-74,3; 108,19</t>
+          <t>-73,84; 109,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-86,4; 208,8</t>
+          <t>-84,27; 220,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,98; 1214,08</t>
+          <t>-54,05; 570,98</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,4</t>
+          <t>0,87; 4,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,48</t>
+          <t>-1,56; 1,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,73</t>
+          <t>-0,08; 1,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 2,36</t>
+          <t>-1,7; 3,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,68; —</t>
+          <t>-0,08; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,69; 265,51</t>
+          <t>-73,79; 300,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,02; 171,65</t>
+          <t>-41,37; 194,24</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>-11,65%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,2</t>
+          <t>-1,36; 1,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 1,56</t>
+          <t>-4,11; 1,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,96</t>
+          <t>0,27; 3,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,91</t>
+          <t>-2,52; 1,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-84,34; 150,57</t>
+          <t>-83,95; 185,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 185,69</t>
+          <t>-68,53; 120,67</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,13</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>500,03%</t>
+          <t>237,15%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,97</t>
+          <t>-2,21; 0,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,85</t>
+          <t>0,02; 3,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,66</t>
+          <t>-1,27; 4,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,25</t>
+          <t>0,07; 2,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 1048,14</t>
+          <t>-13,59; 985,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,91; 274,58</t>
+          <t>-39,66; 246,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,8; —</t>
+          <t>-39,14; —</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-69,89%</t>
+          <t>-46,79%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,84</t>
+          <t>-1,83; 2,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,84</t>
+          <t>-3,74; 3,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,4</t>
+          <t>-0,74; 3,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,28</t>
+          <t>-1,99; 0,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,39; 242,35</t>
+          <t>-68,94; 196,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-2,76%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,62</t>
+          <t>-1,88; 3,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,65</t>
+          <t>-0,4; 2,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,28</t>
+          <t>-2,46; 2,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 684,73</t>
+          <t>-65,26; 404,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 101,73</t>
+          <t>-50,02; 127,97</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,6</t>
+          <t>2,45</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>637,98%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,9</t>
+          <t>-0,98; 0,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,0</t>
+          <t>-1,73; 0,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,32</t>
+          <t>-0,56; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 61,31</t>
+          <t>-0,01; 4,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-82,52; 346,61</t>
+          <t>-85,94; 338,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-68,5; 118,15</t>
+          <t>-70,37; 110,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-72,36; —</t>
+          <t>-66,77; 988,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,2; 2420,22</t>
+          <t>-4,7; 192,73</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>-1,37%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,25</t>
+          <t>-0,91; 1,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,23</t>
+          <t>-0,21; 2,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,55</t>
+          <t>-0,6; 1,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,95</t>
+          <t>-1,49; 1,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 274,78</t>
+          <t>-61,57; 262,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,38; 560,78</t>
+          <t>-26,13; 543,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-43,76; 314,49</t>
+          <t>-55,42; 315,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,39; 286,55</t>
+          <t>-53,33; 87,81</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>288,49%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,76</t>
+          <t>-0,26; 0,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,88</t>
+          <t>-0,46; 0,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,2</t>
+          <t>0,11; 1,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 23,21</t>
+          <t>0,03; 1,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,31; 118,21</t>
+          <t>-26,02; 112,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 57,91</t>
+          <t>-21,21; 64,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,09; 167,0</t>
+          <t>4,71; 172,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>18,79; 1251,88</t>
+          <t>0,47; 80,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_psíq_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_psíq_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad psíquica</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad psíquica</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
